--- a/output/pdf_financials_xlsx/DNO.xlsx
+++ b/output/pdf_financials_xlsx/DNO.xlsx
@@ -1186,19 +1186,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.273792</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.439226</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.349784</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.093984</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.031784</v>
       </c>
     </row>
     <row r="35">
@@ -1230,19 +1230,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.273792</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.439226</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.349784</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.093984</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.031784</v>
       </c>
     </row>
     <row r="37">
@@ -1494,19 +1494,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.273792</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.446137</v>
+        <v>0.006911</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.423186</v>
+        <v>0.073402</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.096493</v>
+        <v>0.002509</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.032317</v>
+        <v>0.0005330000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/DNO.xlsx
+++ b/output/pdf_financials_xlsx/DNO.xlsx
@@ -2665,19 +2665,19 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.000127</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.009601</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>0.003839</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>-0.013205</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.01414</v>
       </c>
     </row>
     <row r="102">
@@ -4319,7 +4319,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>-0.000127</v>
       </c>
